--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-11.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-11.xlsx
@@ -474,682 +474,682 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583999085283</v>
+        <v>5583999673160</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Zarqueu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pedro Henrique dos Santos</t>
+          <t>Zarqueu Manoel da Silva</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5561999948430</v>
+        <v>5583991210505</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>William Lemos</t>
+          <t>Maria Beatriz Lima do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583987451029</v>
+        <v>5583993912051</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Veronica</t>
+          <t>Ricardo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Veronica Alves da Silva</t>
+          <t>Ricardo Lira</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583986420196</v>
+        <v>5583996736779</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gilson</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gilson do Nascimento Oliveira</t>
+          <t>Maria das Dores Silva</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583996245611</v>
+        <v>5583999154417</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cristina</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cristina Cortez</t>
+          <t>Leandro do Nascimento Silva</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583996175312</v>
+        <v>5583991392674</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>Felipe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Julio Cesar Rocha</t>
+          <t>Felipe Pereira</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583987345940</v>
+        <v>5583999085283</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Uninassau</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uninassau Joao Pessoa - Epitacio Pessoa</t>
+          <t>Pedro Henrique dos Santos</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583991731682</v>
+        <v>5561999948430</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Edivaldo</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Edivaldo Gomes</t>
+          <t>William Lemos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583987790656</v>
+        <v>5583987451029</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bruna</t>
+          <t>Veronica</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bruna Cruz de Santana</t>
+          <t>Veronica Alves da Silva</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583988715751</v>
+        <v>5583986420196</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Gilson</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Leonardo Soares Gomes</t>
+          <t>Gilson do Nascimento Oliveira</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583988471569</v>
+        <v>5583996245611</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>Cristina</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eduardo Silva</t>
+          <t>Cristina Cortez</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583991913039</v>
+        <v>5583996175312</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Windison</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Windison Mariano Costa</t>
+          <t>Julio Cesar Rocha</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583987560790</v>
+        <v>5583987345940</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Manoel</t>
+          <t>Uninassau</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Manoel Soares dos Santos</t>
+          <t>Uninassau Joao Pessoa - Epitacio Pessoa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583988909378</v>
+        <v>5583991731682</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Edivaldo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Anderson dos Santos Silva</t>
+          <t>Edivaldo Gomes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583988840200</v>
+        <v>5583987790656</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Iranildo</t>
+          <t>Bruna</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iranildo Rodrigues da Silva</t>
+          <t>Bruna Cruz de Santana</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583993024800</v>
+        <v>5583988715751</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rejane</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rejane Bezerra de Meneses Silva</t>
+          <t>Leonardo Soares Gomes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5592993675681</v>
+        <v>5583988471569</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Viviane</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Viviane da Conceicao Pereira de Oliveira</t>
+          <t>Eduardo Silva</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583986262115</v>
+        <v>5583991913039</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ricky</t>
+          <t>Windison</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ricky dos Santos</t>
+          <t>Windison Mariano Costa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583999855484</v>
+        <v>5583987560790</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fleming</t>
+          <t>Manoel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fleming Cabral</t>
+          <t>Manoel Soares dos Santos</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583998299145</v>
+        <v>5583988909378</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Danielle Pereira da Silva</t>
+          <t>Anderson dos Santos Silva</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583986538580</v>
+        <v>5583988840200</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vanessa</t>
+          <t>Iranildo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vanessa Cavalcante Xavier</t>
+          <t>Iranildo Rodrigues da Silva</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583999831600</v>
+        <v>5583993024800</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nicacio</t>
+          <t>Rejane</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nicacio Oliveira de Sousa</t>
+          <t>Rejane Bezerra de Meneses Silva</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583998881951</v>
+        <v>5592993675681</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>Viviane</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Patricia de Oliveira Barros</t>
+          <t>Viviane da Conceicao Pereira de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583987421436</v>
+        <v>5583986262115</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adriana</t>
+          <t>Ricky</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Adriana Emilia da Conceição</t>
+          <t>Ricky dos Santos</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5521968351614</v>
+        <v>5583999855484</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Luzineide</t>
+          <t>Fleming</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Luzineide Oliveira Dias de Azevedo</t>
+          <t>Fleming Cabral</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583988457370</v>
+        <v>5583998299145</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jose Francisco Galdino</t>
+          <t>Danielle Pereira da Silva</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583987536727</v>
+        <v>5583986538580</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vitor</t>
+          <t>Vanessa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vitor Marques de Oliveira</t>
+          <t>Vanessa Cavalcante Xavier</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583988553925</v>
+        <v>5583999831600</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Raiff</t>
+          <t>Nicacio</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raiff José Nazário Bezerra</t>
+          <t>Nicacio Oliveira de Sousa</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583988975091</v>
+        <v>5583998881951</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Darci</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Darci de Freitas</t>
+          <t>Patricia de Oliveira Barros</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583986945360</v>
+        <v>5583987421436</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mateus</t>
+          <t>Adriana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mateus Silveira Xavier</t>
+          <t>Adriana Emilia da Conceição</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583998341624</v>
+        <v>5521968351614</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Polyana</t>
+          <t>Luzineide</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Polyana Emmily Correia Da�Silva</t>
+          <t>Luzineide Oliveira Dias de Azevedo</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5598985583585</v>
+        <v>5583988457370</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Valdemir</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valdemir Belchior</t>
+          <t>Jose Francisco Galdino</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583987206156</v>
+        <v>5583987536727</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Vitor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Amanda Freire de Lima</t>
+          <t>Vitor Marques de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583996465220</v>
+        <v>5583988553925</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Raiff</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jose Carlos Barbosa da Silva</t>
+          <t>Raiff José Nazário Bezerra</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583999529437</v>
+        <v>5583988975091</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dionatan</t>
+          <t>Darci</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dionatan Toledo</t>
+          <t>Darci de Freitas</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583988575084</v>
+        <v>5583986945360</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tarcila</t>
+          <t>Mateus</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tarcila Fernandes</t>
+          <t>Mateus Silveira Xavier</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583996591125</v>
+        <v>5583998341624</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dw</t>
+          <t>Polyana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dw Pre-Moldados</t>
+          <t>Polyana Emmily Correia Da�Silva</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583999414180</v>
+        <v>5598985583585</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rogerio</t>
+          <t>Valdemir</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rogerio Francisco de Lima</t>
+          <t>Valdemir Belchior</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583986427785</v>
+        <v>5583987206156</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Residencial Maria Emilia</t>
+          <t>Amanda Freire de Lima</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583982167244</v>
+        <v>5583996465220</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Maria do Livramento Silva</t>
+          <t>Jose Carlos Barbosa da Silva</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583987038395</v>
+        <v>5583999529437</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Elizeu</t>
+          <t>Dionatan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Elizeu do Nascimento Pereira</t>
+          <t>Dionatan Toledo</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583988738888</v>
+        <v>5583988575084</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Raimundo</t>
+          <t>Tarcila</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Raimundo Texeira de Souza</t>
+          <t>Tarcila Fernandes</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583988621829</v>
+        <v>5583996591125</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Felipe</t>
+          <t>Dw</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Felipe dos Santos</t>
+          <t>Dw Pre-Moldados</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583988520895</v>
+        <v>5583999414180</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kewen</t>
+          <t>Rogerio</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kewen Vinicius</t>
+          <t>Rogerio Francisco de Lima</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583988212779</v>
+        <v>5583986427785</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jocsiã</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jocsiã dos Santos Moreira</t>
+          <t>Residencial Maria Emilia</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583988295029</v>
+        <v>5583982167244</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1158,67 +1158,67 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Maria Jose Alves de Andrade</t>
+          <t>Maria do Livramento Silva</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583993930086</v>
+        <v>5583987038395</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Italo</t>
+          <t>Elizeu</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italo Ramos</t>
+          <t>Elizeu do Nascimento Pereira</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583986243983</v>
+        <v>5583988738888</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Raimundo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Antonio Valdevino de Melo</t>
+          <t>Raimundo Texeira de Souza</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583986688094</v>
+        <v>5583988621829</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Robeciano</t>
+          <t>Felipe</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Robeciano Luiz da Silva</t>
+          <t>Felipe dos Santos</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583987668630</v>
+        <v>5583988520895</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Adenilza</t>
+          <t>Kewen</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Adenilza Marinho Silva</t>
+          <t>Kewen Vinicius</t>
         </is>
       </c>
     </row>
